--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:43:27+00:00</t>
+    <t>2026-07-01T12:03:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:03:19+00:00</t>
+    <t>2026-07-03T07:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -595,7 +595,7 @@
     <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis|20260420150250</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis|20260619134042</t>
   </si>
   <si>
     <t>OBR-24</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:33:59+00:00</t>
+    <t>2026-07-08T09:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T09:43:12+00:00</t>
+    <t>2026-07-08T10:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
